--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -520,23 +520,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -548,23 +548,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
     </row>
